--- a/tests/sample_data/CEData_Surface.xlsx
+++ b/tests/sample_data/CEData_Surface.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -412,10 +412,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -424,31 +424,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>-37</v>
+        <v>-35</v>
       </c>
       <c r="G2">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="H2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>59800</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -461,24 +461,27 @@
         </is>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>-36</v>
+        <v>-34</v>
       </c>
       <c r="G3">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -491,27 +494,27 @@
         </is>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>-37</v>
+        <v>-33</v>
       </c>
       <c r="G4">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="H4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4">
-        <v>36200</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -524,24 +527,27 @@
         </is>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G5">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>20400</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1976</v>
+        <v>1981</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -554,16 +560,481 @@
         </is>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>-34</v>
       </c>
       <c r="G6">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="H6">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1983</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>-34</v>
+      </c>
+      <c r="G7">
+        <v>120</v>
+      </c>
+      <c r="H7">
+        <v>524</v>
+      </c>
+      <c r="I7">
+        <v>107100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1984</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>-36</v>
+      </c>
+      <c r="G8">
+        <v>150</v>
+      </c>
+      <c r="H8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1987</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>-34</v>
+      </c>
+      <c r="G9">
+        <v>122</v>
+      </c>
+      <c r="H9">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1987</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>-35</v>
+      </c>
+      <c r="G10">
+        <v>117</v>
+      </c>
+      <c r="H10">
+        <v>160</v>
+      </c>
+      <c r="I10">
+        <v>22100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1988</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>-34</v>
+      </c>
+      <c r="G11">
+        <v>119</v>
+      </c>
+      <c r="H11">
+        <v>70</v>
+      </c>
+      <c r="I11">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1990</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>-34</v>
+      </c>
+      <c r="G12">
+        <v>120</v>
+      </c>
+      <c r="H12">
+        <v>136</v>
+      </c>
+      <c r="I12">
+        <v>37100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1991</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>-36</v>
+      </c>
+      <c r="G13">
+        <v>150</v>
+      </c>
+      <c r="H13">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1992</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>-38</v>
+      </c>
+      <c r="G14">
+        <v>148</v>
+      </c>
+      <c r="H14">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>1994</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>-36</v>
+      </c>
+      <c r="G15">
+        <v>150</v>
+      </c>
+      <c r="H15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2004</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>-37</v>
+      </c>
+      <c r="G16">
+        <v>150</v>
+      </c>
+      <c r="H16">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>-34</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2016</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>-36</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>2016</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>9</v>
+      </c>
+      <c r="F19">
+        <v>-36</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>2018</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+      <c r="F20">
+        <v>-32</v>
+      </c>
+      <c r="G20">
+        <v>15</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>2018</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>15</v>
+      </c>
+      <c r="F21">
+        <v>-32</v>
+      </c>
+      <c r="G21">
+        <v>18</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
